--- a/data/UOL_MoU_Country_Previous.xlsx
+++ b/data/UOL_MoU_Country_Previous.xlsx
@@ -2,36 +2,36 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Rcf005fca494e4e3a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All Separated Activities" sheetId="2" r:id="R08b94d1d4efe4d70"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Alumni Talk - Mentoring" sheetId="3" r:id="R1f7675dcc8cf44f2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Community Engagement" sheetId="4" r:id="Rc72c8ae826574719"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Conference" sheetId="5" r:id="R743d7fd8328c4e8d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Curriculum Feedback Session" sheetId="6" r:id="R649a32c68a714fd5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GLIT" sheetId="7" r:id="R13aeac5e7f8040c5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guest Lecture" sheetId="8" r:id="R59f3179e71ef4a39"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IAB Meeting - Industry Consulta" sheetId="9" r:id="R6fa858a082744942"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IP" sheetId="10" r:id="Ra514ecf379dd478e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IV" sheetId="11" r:id="Ra780fb6650fd4a40"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Industrial Visit" sheetId="12" r:id="R8d5b0f090f9649a8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Internship-Placement" sheetId="13" r:id="Re46815b1d3924748"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MOU" sheetId="14" r:id="Rf6dae37414284e76"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MoU Signing (Memorandum of Unde" sheetId="15" r:id="R43ffabe6e88c41cb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Others" sheetId="16" r:id="Rb5cad066f01243b0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Research Collaboration" sheetId="17" r:id="R28bcc7f6ae874206"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Seminar" sheetId="18" r:id="R22ef3717c4654fe7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Unclassified" sheetId="19" r:id="R337c48f76c2c4cfd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Workshop" sheetId="20" r:id="R1863ffbd118f4ae1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guest Lecture - GLIT" sheetId="21" r:id="R488eed915d514785"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Industrial Visit - IV" sheetId="22" r:id="R49c76a0a767e4486"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Internship - Placement" sheetId="23" r:id="R862219762e484895"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MoU - MoU Signing" sheetId="24" r:id="R1a1a869b63f94f9d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="New Data Added" sheetId="25" r:id="Rae4346d64e1043eb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Planned - Section 4" sheetId="26" r:id="R4aff43e32b5f4323"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Planned Activities" sheetId="27" r:id="Raf89825df5dc4cdb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remote Activities" sheetId="28" r:id="R4e1c71387f0e4f45"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MoU Country (No Nulls)" sheetId="29" r:id="Re91a311b4e9744e6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MoU Country Summary" sheetId="30" r:id="R3303427c48594aaf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Rdad80da6f9604d0f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All Separated Activities" sheetId="2" r:id="R80ced7a8b62146e0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Alumni Talk - Mentoring" sheetId="3" r:id="R38af0d0b386a4aaa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Community Engagement" sheetId="4" r:id="R4d8a748495e24f06"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Conference" sheetId="5" r:id="R5a7608fa638d4a98"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Curriculum Feedback Session" sheetId="6" r:id="R0cdff558b0a841cd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GLIT" sheetId="7" r:id="Ref6fd6410a2e4657"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guest Lecture" sheetId="8" r:id="R246c4d5251414f55"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IAB Meeting - Industry Consulta" sheetId="9" r:id="Rd5b696e66e76481f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IP" sheetId="10" r:id="R3f1f8bc7f9824164"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IV" sheetId="11" r:id="R5cff6cc6c6384db7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Industrial Visit" sheetId="12" r:id="R0e329e8720c9428a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Internship-Placement" sheetId="13" r:id="Rc2fbd411b06f4fba"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MOU" sheetId="14" r:id="R3b3e87ab8c1a4e2a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MoU Signing (Memorandum of Unde" sheetId="15" r:id="R97eec49242d144ae"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Others" sheetId="16" r:id="R9432663e60f243da"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Research Collaboration" sheetId="17" r:id="Rca391211aefc4c75"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Seminar" sheetId="18" r:id="R3af65d1039954eaf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Unclassified" sheetId="19" r:id="Rd1ce5b0d7c4346bb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Workshop" sheetId="20" r:id="Rd871a193ff5740b0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guest Lecture - GLIT" sheetId="21" r:id="R3b138344369f4faf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Industrial Visit - IV" sheetId="22" r:id="R02aa3399a16346e7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Internship - Placement" sheetId="23" r:id="R823be75b83ab498d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MoU - MoU Signing" sheetId="24" r:id="Rd437cbf10e5042e3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="New Data Added" sheetId="25" r:id="R0247b888fae54dc3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Planned - Section 4" sheetId="26" r:id="Rae50c8c0c72a4402"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Planned Activities" sheetId="27" r:id="R0185b2dcbe9f4d6e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remote Activities" sheetId="28" r:id="R5c3b7ca5f33142ab"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MoU Country (No Nulls)" sheetId="29" r:id="R60ba26d37b1f4d5b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MoU Country Summary" sheetId="30" r:id="Raa8745d5ce8b4451"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -47871,6 +47871,84 @@
         <x:v>Partner Institution: WWF, Country: Pakistan, MOU Type: NGO, Key Activities: Knowledge Sharing, Status: Completed</x:v>
       </x:c>
     </x:row>
+    <x:row r="30">
+      <x:c r="A30" t="str">
+        <x:v>PRPSTFPT103</x:v>
+      </x:c>
+      <x:c r="B30" t="str">
+        <x:v>Faculty of Arts and Architecture</x:v>
+      </x:c>
+      <x:c r="C30" t="str">
+        <x:v>School of Creative Arts</x:v>
+      </x:c>
+      <x:c r="D30" t="str">
+        <x:v>IRC</x:v>
+      </x:c>
+      <x:c r="E30" t="str">
+        <x:v>Pakistan</x:v>
+      </x:c>
+      <x:c r="F30" t="str">
+        <x:v>Academic</x:v>
+      </x:c>
+      <x:c r="G30" t="str">
+        <x:v>Not Started</x:v>
+      </x:c>
+      <x:c r="H30" t="str">
+        <x:v>Partner Institution: IRC, Country: Pakistan, MOU Type: Academic, Key Activities: Yes, Status: Not Started</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" t="str">
+        <x:v>PRPSTFPT100</x:v>
+      </x:c>
+      <x:c r="B31" t="str">
+        <x:v>Faculty of Social Sciences</x:v>
+      </x:c>
+      <x:c r="C31" t="str">
+        <x:v>School of Integrated Social Science</x:v>
+      </x:c>
+      <x:c r="D31" t="str">
+        <x:v>The Golden Ring Economic Forum</x:v>
+      </x:c>
+      <x:c r="E31" t="str">
+        <x:v>Pakistan</x:v>
+      </x:c>
+      <x:c r="F31" t="str">
+        <x:v>Industry</x:v>
+      </x:c>
+      <x:c r="G31" t="str">
+        <x:v>Completed</x:v>
+      </x:c>
+      <x:c r="H31" t="str">
+        <x:v>Partner Institution: The Golden Ring Economic Forum, Country: Pakistan, MOU Type: Industry, Key Activities: Research Collaboration, Status: Completed, Evidence: files::6abf4e0dca9ef_GREF.pdf</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" t="str">
+        <x:v>PRPSTFPT100</x:v>
+      </x:c>
+      <x:c r="B32" t="str">
+        <x:v>Faculty of Social Sciences</x:v>
+      </x:c>
+      <x:c r="C32" t="str">
+        <x:v>School of Integrated Social Science</x:v>
+      </x:c>
+      <x:c r="D32" t="str">
+        <x:v>Consortium for Asia Pacific &amp; Eurasian Studies (CAPES)</x:v>
+      </x:c>
+      <x:c r="E32" t="str">
+        <x:v>Pakistan</x:v>
+      </x:c>
+      <x:c r="F32" t="str">
+        <x:v>Academic</x:v>
+      </x:c>
+      <x:c r="G32" t="str">
+        <x:v>Completed</x:v>
+      </x:c>
+      <x:c r="H32" t="str">
+        <x:v>Partner Institution: Consortium for Asia Pacific &amp; Eurasian Studies (CAPES), Country: Pakistan, MOU Type: Academic, Key Activities: Research Collaboration, Fellowship Hosting, Status: Completed, Evidence: files::6abf4e22c66dc_CAPES.pdf</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
